--- a/IncreasedSamplingIndirectBP/OverallStatsIncreasedSamplingIndirectBP-noboot.xlsx
+++ b/IncreasedSamplingIndirectBP/OverallStatsIncreasedSamplingIndirectBP-noboot.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexb\OneDrive\Documents\Thesis\IncreasedSamplingIndirectBP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8631CDBD-CC33-4EB5-B6BA-5C8D9545C56C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05C7976D-2F94-4762-BA3A-3F403A151AB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3040" yWindow="3040" windowWidth="28800" windowHeight="14460" xr2:uid="{84A3B88E-B226-40B3-A64E-0FDCC502A4B5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{84A3B88E-B226-40B3-A64E-0FDCC502A4B5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,9 +38,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
-    <t>HalfCache</t>
-  </si>
-  <si>
     <t>Program</t>
   </si>
   <si>
@@ -96,6 +93,9 @@
   </si>
   <si>
     <t>Nu: 0.0001, Gamma: 0.0001</t>
+  </si>
+  <si>
+    <t>IndirectBP</t>
   </si>
 </sst>
 </file>
@@ -478,56 +478,56 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>8</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" t="s">
         <v>9</v>
       </c>
-      <c r="H2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>10</v>
-      </c>
-      <c r="M2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -569,10 +569,10 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -614,10 +614,10 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C13">
         <v>1</v>
